--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:14:54+00:00</t>
+    <t>2023-11-28T12:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:15:35+00:00</t>
+    <t>2023-11-28T12:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:22:20+00:00</t>
+    <t>2023-11-28T12:44:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:44:29+00:00</t>
+    <t>2023-11-28T13:07:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:07:26+00:00</t>
+    <t>2023-11-28T13:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:18:47+00:00</t>
+    <t>2023-11-28T13:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:27:45+00:00</t>
+    <t>2023-11-28T13:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:42:11+00:00</t>
+    <t>2023-12-08T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T10:33:05+00:00</t>
+    <t>2023-12-29T10:04:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:04:05+00:00</t>
+    <t>2024-02-01T10:35:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T10:35:02+00:00</t>
+    <t>2024-02-01T13:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:55:30+00:00</t>
+    <t>2024-02-01T13:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:56:11+00:00</t>
+    <t>2024-02-01T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T14:29:51+00:00</t>
+    <t>2024-02-01T16:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T16:04:25+00:00</t>
+    <t>2024-02-05T14:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:48:49+00:00</t>
+    <t>2024-02-12T14:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:46:58+00:00</t>
+    <t>2024-02-12T14:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/main/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:53:29+00:00</t>
+    <t>2024-04-08T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
